--- a/tt_drama_performance/data/content_performance_2026-08-18.xlsx
+++ b/tt_drama_performance/data/content_performance_2026-08-18.xlsx
@@ -433,13 +433,13 @@
         <v>Seduced by the Dark Lord I Swore To Kill</v>
       </c>
       <c r="C2">
-        <v>6085</v>
+        <v>6371</v>
       </c>
       <c r="D2">
-        <v>17572</v>
+        <v>18408</v>
       </c>
       <c r="E2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F2">
         <v>55</v>
@@ -448,7 +448,7 @@
         <v>5</v>
       </c>
       <c r="H2">
-        <v>326</v>
+        <v>359</v>
       </c>
     </row>
     <row r="3">
@@ -459,22 +459,22 @@
         <v>The Fallen Elf Prince Returns</v>
       </c>
       <c r="C3">
-        <v>257287</v>
+        <v>267113</v>
       </c>
       <c r="D3">
-        <v>652031</v>
+        <v>668424</v>
       </c>
       <c r="E3">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F3">
-        <v>3440</v>
+        <v>3477</v>
       </c>
       <c r="G3">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H3">
-        <v>15487</v>
+        <v>15772</v>
       </c>
     </row>
     <row r="4">
@@ -485,22 +485,22 @@
         <v>Perfect Housewife's Deadly Secret</v>
       </c>
       <c r="C4">
-        <v>20057</v>
+        <v>20220</v>
       </c>
       <c r="D4">
-        <v>88599</v>
+        <v>89134</v>
       </c>
       <c r="E4">
         <v>46</v>
       </c>
       <c r="F4">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G4">
         <v>8</v>
       </c>
       <c r="H4">
-        <v>1013</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="5">
@@ -511,22 +511,22 @@
         <v>My Rich Husband's Forbidden Love</v>
       </c>
       <c r="C5">
-        <v>725765</v>
+        <v>731966</v>
       </c>
       <c r="D5">
-        <v>1424519</v>
+        <v>1435190</v>
       </c>
       <c r="E5">
         <v>63</v>
       </c>
       <c r="F5">
-        <v>1763</v>
+        <v>1777</v>
       </c>
       <c r="G5">
         <v>103</v>
       </c>
       <c r="H5">
-        <v>9030</v>
+        <v>9126</v>
       </c>
     </row>
     <row r="6">
@@ -537,10 +537,10 @@
         <v>My CEO Loves My Voice</v>
       </c>
       <c r="C6">
-        <v>225273</v>
+        <v>225655</v>
       </c>
       <c r="D6">
-        <v>676841</v>
+        <v>677601</v>
       </c>
       <c r="E6">
         <v>35</v>
@@ -552,7 +552,7 @@
         <v>86</v>
       </c>
       <c r="H6">
-        <v>5884</v>
+        <v>5891</v>
       </c>
     </row>
     <row r="7">
@@ -563,22 +563,22 @@
         <v>Carmill</v>
       </c>
       <c r="C7">
-        <v>80932</v>
+        <v>81094</v>
       </c>
       <c r="D7">
-        <v>303160</v>
+        <v>303550</v>
       </c>
       <c r="E7">
         <v>46</v>
       </c>
       <c r="F7">
-        <v>1324</v>
+        <v>1327</v>
       </c>
       <c r="G7">
         <v>49</v>
       </c>
       <c r="H7">
-        <v>4582</v>
+        <v>4584</v>
       </c>
     </row>
     <row r="8">
@@ -589,22 +589,22 @@
         <v>Princess Of Mars</v>
       </c>
       <c r="C8">
-        <v>15772747</v>
+        <v>15812272</v>
       </c>
       <c r="D8">
-        <v>46006090</v>
+        <v>46072902</v>
       </c>
       <c r="E8">
         <v>90</v>
       </c>
       <c r="F8">
-        <v>114510</v>
+        <v>114669</v>
       </c>
       <c r="G8">
-        <v>7649</v>
+        <v>7652</v>
       </c>
       <c r="H8">
-        <v>1050959</v>
+        <v>1052426</v>
       </c>
     </row>
     <row r="9">
@@ -641,10 +641,10 @@
         <v>Meu Ama Minha Voz</v>
       </c>
       <c r="C10">
-        <v>17699</v>
+        <v>17701</v>
       </c>
       <c r="D10">
-        <v>68550</v>
+        <v>68558</v>
       </c>
       <c r="E10">
         <v>46</v>
@@ -667,22 +667,22 @@
         <v>My CEO Loves Voice</v>
       </c>
       <c r="C11">
-        <v>7718919</v>
+        <v>7728782</v>
       </c>
       <c r="D11">
-        <v>19188465</v>
+        <v>19223345</v>
       </c>
       <c r="E11">
         <v>75</v>
       </c>
       <c r="F11">
-        <v>80707</v>
+        <v>80850</v>
       </c>
       <c r="G11">
         <v>2545</v>
       </c>
       <c r="H11">
-        <v>283577</v>
+        <v>283788</v>
       </c>
     </row>
     <row r="12">
@@ -693,16 +693,16 @@
         <v>Meu CEO Ama Minha Voz</v>
       </c>
       <c r="C12">
-        <v>28902</v>
+        <v>28951</v>
       </c>
       <c r="D12">
-        <v>99626</v>
+        <v>99697</v>
       </c>
       <c r="E12">
         <v>18</v>
       </c>
       <c r="F12">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G12">
         <v>10</v>
@@ -719,22 +719,22 @@
         <v>Reborn For the Crown</v>
       </c>
       <c r="C13">
-        <v>23589683</v>
+        <v>23626260</v>
       </c>
       <c r="D13">
-        <v>66929488</v>
+        <v>67026556</v>
       </c>
       <c r="E13">
         <v>64</v>
       </c>
       <c r="F13">
-        <v>284029</v>
+        <v>284228</v>
       </c>
       <c r="G13">
-        <v>10120</v>
+        <v>10123</v>
       </c>
       <c r="H13">
-        <v>1350106</v>
+        <v>1351139</v>
       </c>
     </row>
     <row r="14">
@@ -745,22 +745,22 @@
         <v>Falling for a SUPERSTAR 2</v>
       </c>
       <c r="C14">
-        <v>16820151</v>
+        <v>16823374</v>
       </c>
       <c r="D14">
-        <v>38274741</v>
+        <v>38295817</v>
       </c>
       <c r="E14">
         <v>87</v>
       </c>
       <c r="F14">
-        <v>245665</v>
+        <v>245759</v>
       </c>
       <c r="G14">
-        <v>9266</v>
+        <v>9271</v>
       </c>
       <c r="H14">
-        <v>878913</v>
+        <v>879176</v>
       </c>
     </row>
     <row r="15">
@@ -774,7 +774,7 @@
         <v>167729</v>
       </c>
       <c r="D15">
-        <v>486467</v>
+        <v>486474</v>
       </c>
       <c r="E15">
         <v>72</v>
@@ -797,10 +797,10 @@
         <v>Dogfather第一季</v>
       </c>
       <c r="C16">
-        <v>623559</v>
+        <v>623723</v>
       </c>
       <c r="D16">
-        <v>1358435</v>
+        <v>1358660</v>
       </c>
       <c r="E16">
         <v>104</v>
@@ -823,22 +823,22 @@
         <v>MAFIA HUSBAND, DETECTIVE BOYFRIEND</v>
       </c>
       <c r="C17">
-        <v>1614119</v>
+        <v>1616048</v>
       </c>
       <c r="D17">
-        <v>6808328</v>
+        <v>6826163</v>
       </c>
       <c r="E17">
         <v>28</v>
       </c>
       <c r="F17">
-        <v>11450</v>
+        <v>11463</v>
       </c>
       <c r="G17">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="H17">
-        <v>72538</v>
+        <v>72617</v>
       </c>
     </row>
     <row r="18">
@@ -849,22 +849,22 @@
         <v>CEO and the Country Girl</v>
       </c>
       <c r="C18">
-        <v>67651136</v>
+        <v>67787482</v>
       </c>
       <c r="D18">
-        <v>130444649</v>
+        <v>130860988</v>
       </c>
       <c r="E18">
         <v>66</v>
       </c>
       <c r="F18">
-        <v>328843</v>
+        <v>329639</v>
       </c>
       <c r="G18">
-        <v>8000</v>
+        <v>8018</v>
       </c>
       <c r="H18">
-        <v>1619051</v>
+        <v>1623395</v>
       </c>
     </row>
     <row r="19">
@@ -875,22 +875,22 @@
         <v>Revenge of the Wedding Planner</v>
       </c>
       <c r="C19">
-        <v>1975814</v>
+        <v>1978362</v>
       </c>
       <c r="D19">
-        <v>3057176</v>
+        <v>3061544</v>
       </c>
       <c r="E19">
         <v>124</v>
       </c>
       <c r="F19">
-        <v>12134</v>
+        <v>12151</v>
       </c>
       <c r="G19">
         <v>438</v>
       </c>
       <c r="H19">
-        <v>63617</v>
+        <v>63751</v>
       </c>
     </row>
     <row r="20">
@@ -901,22 +901,22 @@
         <v>Taste of You</v>
       </c>
       <c r="C20">
-        <v>9379093</v>
+        <v>9380287</v>
       </c>
       <c r="D20">
-        <v>15569404</v>
+        <v>15571302</v>
       </c>
       <c r="E20">
         <v>66</v>
       </c>
       <c r="F20">
-        <v>42108</v>
+        <v>42121</v>
       </c>
       <c r="G20">
         <v>1019</v>
       </c>
       <c r="H20">
-        <v>192226</v>
+        <v>192295</v>
       </c>
     </row>
     <row r="21">
@@ -927,22 +927,22 @@
         <v>Demon's Kiss</v>
       </c>
       <c r="C21">
-        <v>411066</v>
+        <v>412997</v>
       </c>
       <c r="D21">
-        <v>2620060</v>
+        <v>2622024</v>
       </c>
       <c r="E21">
         <v>16</v>
       </c>
       <c r="F21">
-        <v>3291</v>
+        <v>3297</v>
       </c>
       <c r="G21">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H21">
-        <v>18765</v>
+        <v>18793</v>
       </c>
     </row>
     <row r="22">
@@ -953,22 +953,22 @@
         <v>Thread of Fate</v>
       </c>
       <c r="C22">
-        <v>5118015</v>
+        <v>5119293</v>
       </c>
       <c r="D22">
-        <v>7031405</v>
+        <v>7032851</v>
       </c>
       <c r="E22">
         <v>165</v>
       </c>
       <c r="F22">
-        <v>28699</v>
+        <v>28703</v>
       </c>
       <c r="G22">
         <v>827</v>
       </c>
       <c r="H22">
-        <v>143200</v>
+        <v>143205</v>
       </c>
     </row>
     <row r="23">
@@ -979,22 +979,22 @@
         <v>The Knight and the Influencer</v>
       </c>
       <c r="C23">
-        <v>1030086</v>
+        <v>1030292</v>
       </c>
       <c r="D23">
-        <v>2434195</v>
+        <v>2434533</v>
       </c>
       <c r="E23">
         <v>69</v>
       </c>
       <c r="F23">
-        <v>14460</v>
+        <v>14462</v>
       </c>
       <c r="G23">
         <v>803</v>
       </c>
       <c r="H23">
-        <v>88500</v>
+        <v>88505</v>
       </c>
     </row>
     <row r="24">
@@ -1005,22 +1005,22 @@
         <v>Teaching my Robot Boyfriend How to Love</v>
       </c>
       <c r="C24">
-        <v>1111688</v>
+        <v>1111922</v>
       </c>
       <c r="D24">
-        <v>2629548</v>
+        <v>2629859</v>
       </c>
       <c r="E24">
         <v>53</v>
       </c>
       <c r="F24">
-        <v>5482</v>
+        <v>5487</v>
       </c>
       <c r="G24">
         <v>212</v>
       </c>
       <c r="H24">
-        <v>28859</v>
+        <v>28863</v>
       </c>
     </row>
     <row r="25">
@@ -1031,22 +1031,22 @@
         <v>Behind the Glory of the Runway</v>
       </c>
       <c r="C25">
-        <v>269983</v>
+        <v>270267</v>
       </c>
       <c r="D25">
-        <v>617058</v>
+        <v>617356</v>
       </c>
       <c r="E25">
         <v>79</v>
       </c>
       <c r="F25">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="G25">
         <v>165</v>
       </c>
       <c r="H25">
-        <v>5489</v>
+        <v>5493</v>
       </c>
     </row>
     <row r="26">
@@ -1057,22 +1057,22 @@
         <v>Revenge of the Abandoned Heiress</v>
       </c>
       <c r="C26">
-        <v>540696</v>
+        <v>541148</v>
       </c>
       <c r="D26">
-        <v>1730722</v>
+        <v>1732295</v>
       </c>
       <c r="E26">
         <v>82</v>
       </c>
       <c r="F26">
-        <v>10191</v>
+        <v>10199</v>
       </c>
       <c r="G26">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H26">
-        <v>28305</v>
+        <v>28317</v>
       </c>
     </row>
   </sheetData>
